--- a/thaco/color/1_DATA_MID_Hours.xlsx
+++ b/thaco/color/1_DATA_MID_Hours.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36678CF2-C588-434D-859B-749744F99DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA28FEE-08DA-9D49-A34E-9473C3914757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39160" yWindow="500" windowWidth="33940" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2648,7 +2648,7 @@
     <definedName name="PRESS">#REF!</definedName>
     <definedName name="PRICE">#REF!</definedName>
     <definedName name="PRICE1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng lương tạm ứng kỳ 1'!$A$1:$R$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng lương tạm ứng kỳ 1'!$B$1:$S$20</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="PRINT_AREA_MI1">#REF!</definedName>
     <definedName name="Print_CEM_cc5">#REF!</definedName>
@@ -4180,7 +4180,6 @@
     <definedName name="解_任_">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4197,7 +4196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Actual work day month</t>
   </si>
@@ -4272,6 +4271,18 @@
   </si>
   <si>
     <t>2006324</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -4648,33 +4659,33 @@
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -4687,7 +4698,57 @@
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5051,21 +5112,21 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="37" customWidth="1"/>
-    <col min="2" max="15" width="7.1640625" style="39" customWidth="1"/>
-    <col min="16" max="18" width="10.5" style="38" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="40" customWidth="1"/>
-    <col min="20" max="20" width="12.33203125" style="40" customWidth="1"/>
-    <col min="21" max="21" width="12.5" style="40" customWidth="1"/>
-    <col min="22" max="22" width="11.6640625" style="40" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" style="40" customWidth="1"/>
-    <col min="24" max="16384" width="9.1640625" style="40"/>
+    <col min="1" max="2" width="8.5" style="37" customWidth="1"/>
+    <col min="3" max="16" width="7.1640625" style="39" customWidth="1"/>
+    <col min="17" max="19" width="10.5" style="38" customWidth="1"/>
+    <col min="20" max="20" width="19.5" style="40" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" style="40" customWidth="1"/>
+    <col min="22" max="22" width="12.5" style="40" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" style="40" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="40" customWidth="1"/>
+    <col min="25" max="16384" width="9.1640625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5078,14 +5139,15 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="3"/>
+      <c r="M1" s="2"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="2"/>
+      <c r="P1" s="3"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:23" s="1" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="2" spans="1:24" s="1" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5104,10 +5166,11 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="3" spans="1:24" s="1" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
+      <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -5121,13 +5184,14 @@
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="5"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:23" s="1" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:24" s="1" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -5137,176 +5201,183 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
-      <c r="P4" s="6"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
     </row>
-    <row r="5" spans="1:23" s="10" customFormat="1" ht="19.25" customHeight="1" collapsed="1">
-      <c r="A5" s="48" t="s">
+    <row r="5" spans="1:24" s="10" customFormat="1" ht="19.25" customHeight="1" collapsed="1">
+      <c r="A5" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="C5" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="43" t="s">
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="44"/>
-      <c r="V5" s="11"/>
+      <c r="S5" s="52"/>
       <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:23" s="10" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="45" t="s">
+    <row r="6" spans="1:24" s="10" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="D6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="E6" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="F6" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="G6" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="H6" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="I6" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="J6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="K6" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="45" t="s">
+      <c r="L6" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="45" t="s">
+      <c r="M6" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="53" t="s">
+      <c r="N6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="45" t="s">
+      <c r="O6" s="52"/>
+      <c r="P6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="49" t="s">
+      <c r="Q6" s="42"/>
+      <c r="R6" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="49" t="s">
+      <c r="S6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="V6" s="11"/>
       <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:23" s="12" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="50" t="s">
+    <row r="7" spans="1:24" s="12" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="1" t="s">
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="V7" s="11"/>
       <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:23" s="12" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="13" t="s">
+    <row r="8" spans="1:24" s="12" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="O8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="1">
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="45"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="1">
         <v>25</v>
       </c>
-      <c r="T8" s="14"/>
-      <c r="V8" s="11"/>
+      <c r="U8" s="14"/>
       <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="9" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A9" s="16">
+        <v>1</v>
+      </c>
+      <c r="B9" s="16">
         <v>2405236</v>
       </c>
-      <c r="B9" s="17">
+      <c r="C9" s="17">
         <v>11</v>
       </c>
-      <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
-      <c r="F9" s="17">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17">
         <v>2</v>
       </c>
-      <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="17">
-        <v>0</v>
-      </c>
+      <c r="I9" s="17"/>
       <c r="J9" s="17">
         <v>0</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17">
+      <c r="K9" s="17">
         <v>0</v>
       </c>
+      <c r="L9" s="17"/>
       <c r="M9" s="17">
         <v>0</v>
       </c>
@@ -5316,42 +5387,45 @@
       <c r="O9" s="17">
         <v>0</v>
       </c>
-      <c r="P9" s="18"/>
+      <c r="P9" s="17">
+        <v>0</v>
+      </c>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="20"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="19"/>
       <c r="U9" s="20"/>
-      <c r="V9" s="21"/>
+      <c r="V9" s="20"/>
       <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
     </row>
-    <row r="10" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="10" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A10" s="16">
+        <v>2</v>
+      </c>
+      <c r="B10" s="16">
         <v>2106723</v>
       </c>
-      <c r="B10" s="17">
+      <c r="C10" s="17">
         <v>10.5</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17">
         <v>0.5</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17">
         <v>2</v>
       </c>
-      <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="17">
-        <v>0</v>
-      </c>
+      <c r="I10" s="17"/>
       <c r="J10" s="17">
         <v>0</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17">
+      <c r="K10" s="17">
         <v>0</v>
       </c>
+      <c r="L10" s="17"/>
       <c r="M10" s="17">
         <v>0</v>
       </c>
@@ -5361,40 +5435,43 @@
       <c r="O10" s="17">
         <v>0</v>
       </c>
-      <c r="P10" s="18"/>
+      <c r="P10" s="17">
+        <v>0</v>
+      </c>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="20"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="19"/>
       <c r="U10" s="20"/>
-      <c r="V10" s="21"/>
+      <c r="V10" s="20"/>
       <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
     </row>
-    <row r="11" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="11" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A11" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="17">
+      <c r="C11" s="17">
         <v>11</v>
       </c>
-      <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
-      <c r="F11" s="17">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17">
         <v>2</v>
       </c>
-      <c r="G11" s="17"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="17">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17">
         <v>4</v>
       </c>
-      <c r="J11" s="17">
+      <c r="K11" s="17">
         <v>0</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17">
-        <v>0</v>
-      </c>
+      <c r="L11" s="17"/>
       <c r="M11" s="17">
         <v>0</v>
       </c>
@@ -5404,42 +5481,45 @@
       <c r="O11" s="17">
         <v>0</v>
       </c>
-      <c r="P11" s="18"/>
+      <c r="P11" s="17">
+        <v>0</v>
+      </c>
       <c r="Q11" s="18"/>
       <c r="R11" s="18"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="20"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="19"/>
       <c r="U11" s="20"/>
-      <c r="V11" s="21"/>
+      <c r="V11" s="20"/>
       <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
     </row>
-    <row r="12" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="12" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A12" s="16">
+        <v>4</v>
+      </c>
+      <c r="B12" s="16">
         <v>2406198</v>
       </c>
-      <c r="B12" s="17">
+      <c r="C12" s="17">
         <v>10.5</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17">
         <v>0.5</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17">
+      <c r="F12" s="17"/>
+      <c r="G12" s="17">
         <v>2</v>
       </c>
-      <c r="G12" s="17"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
+      <c r="I12" s="17"/>
       <c r="J12" s="17">
         <v>0</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17">
+      <c r="K12" s="17">
         <v>0</v>
       </c>
+      <c r="L12" s="17"/>
       <c r="M12" s="17">
         <v>0</v>
       </c>
@@ -5449,40 +5529,43 @@
       <c r="O12" s="17">
         <v>0</v>
       </c>
-      <c r="P12" s="18"/>
+      <c r="P12" s="17">
+        <v>0</v>
+      </c>
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="20"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="19"/>
       <c r="U12" s="20"/>
-      <c r="V12" s="21"/>
+      <c r="V12" s="20"/>
       <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
     </row>
-    <row r="13" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="13" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A13" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="17">
+      <c r="C13" s="17">
         <v>11</v>
       </c>
-      <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
-      <c r="F13" s="17">
+      <c r="F13" s="17"/>
+      <c r="G13" s="17">
         <v>2</v>
       </c>
-      <c r="G13" s="17"/>
       <c r="H13" s="17"/>
-      <c r="I13" s="17">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17">
         <v>4</v>
       </c>
-      <c r="J13" s="17">
+      <c r="K13" s="17">
         <v>0</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17">
-        <v>0</v>
-      </c>
+      <c r="L13" s="17"/>
       <c r="M13" s="17">
         <v>0</v>
       </c>
@@ -5492,42 +5575,45 @@
       <c r="O13" s="17">
         <v>0</v>
       </c>
-      <c r="P13" s="18"/>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
       <c r="Q13" s="18"/>
       <c r="R13" s="18"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="20"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="19"/>
       <c r="U13" s="20"/>
-      <c r="V13" s="21"/>
+      <c r="V13" s="20"/>
       <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
     </row>
-    <row r="14" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="14" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A14" s="16">
+        <v>6</v>
+      </c>
+      <c r="B14" s="16">
         <v>2406145</v>
       </c>
-      <c r="B14" s="17">
+      <c r="C14" s="17">
         <v>10.5</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17">
         <v>0.5</v>
       </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17">
         <v>2</v>
       </c>
-      <c r="G14" s="17"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="17">
-        <v>0</v>
-      </c>
+      <c r="I14" s="17"/>
       <c r="J14" s="17">
         <v>0</v>
       </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17">
+      <c r="K14" s="17">
         <v>0</v>
       </c>
+      <c r="L14" s="17"/>
       <c r="M14" s="17">
         <v>0</v>
       </c>
@@ -5537,40 +5623,43 @@
       <c r="O14" s="17">
         <v>0</v>
       </c>
-      <c r="P14" s="18"/>
+      <c r="P14" s="17">
+        <v>0</v>
+      </c>
       <c r="Q14" s="18"/>
       <c r="R14" s="18"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="20"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="19"/>
       <c r="U14" s="20"/>
-      <c r="V14" s="21"/>
+      <c r="V14" s="20"/>
       <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
     </row>
-    <row r="15" spans="1:23" s="15" customFormat="1" ht="30.5" customHeight="1">
+    <row r="15" spans="1:24" s="15" customFormat="1" ht="30.5" customHeight="1">
       <c r="A15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="17">
+      <c r="C15" s="17">
         <v>11</v>
       </c>
-      <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="17">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17">
         <v>2</v>
       </c>
-      <c r="G15" s="17"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="17">
+      <c r="I15" s="17"/>
+      <c r="J15" s="17">
         <v>4</v>
       </c>
-      <c r="J15" s="17">
+      <c r="K15" s="17">
         <v>0</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
+      <c r="L15" s="17"/>
       <c r="M15" s="17">
         <v>0</v>
       </c>
@@ -5580,18 +5669,21 @@
       <c r="O15" s="17">
         <v>0</v>
       </c>
-      <c r="P15" s="18"/>
+      <c r="P15" s="17">
+        <v>0</v>
+      </c>
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="20"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="19"/>
       <c r="U15" s="20"/>
-      <c r="V15" s="21"/>
+      <c r="V15" s="20"/>
       <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
     </row>
-    <row r="16" spans="1:23" s="23" customFormat="1" ht="18.75" customHeight="1">
+    <row r="16" spans="1:24" s="23" customFormat="1" ht="18.75" customHeight="1">
       <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
@@ -5601,85 +5693,98 @@
       <c r="I16" s="25"/>
       <c r="J16" s="25"/>
       <c r="K16" s="25"/>
-      <c r="L16" s="26"/>
+      <c r="L16" s="25"/>
       <c r="M16" s="26"/>
-      <c r="N16" s="27"/>
+      <c r="N16" s="26"/>
       <c r="O16" s="27"/>
-      <c r="P16" s="28"/>
+      <c r="P16" s="27"/>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="T16" s="29"/>
+      <c r="S16" s="28"/>
+      <c r="U16" s="29"/>
     </row>
-    <row r="17" spans="1:20" s="30" customFormat="1" ht="21" customHeight="1">
+    <row r="17" spans="1:21" s="30" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="31"/>
-      <c r="B17" s="32"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="31"/>
+      <c r="I17" s="32"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="32"/>
       <c r="O17" s="31"/>
       <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
       <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
     </row>
-    <row r="18" spans="1:20" s="30" customFormat="1" ht="18" customHeight="1">
+    <row r="18" spans="1:21" s="30" customFormat="1" ht="18" customHeight="1">
       <c r="A18" s="34"/>
-      <c r="B18" s="33"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="33"/>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
-      <c r="I18" s="32"/>
-      <c r="L18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="32"/>
       <c r="M18" s="33"/>
-      <c r="N18" s="35"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="35"/>
-      <c r="T18" s="36"/>
+      <c r="P18" s="35"/>
+      <c r="U18" s="36"/>
     </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1">
-      <c r="O19" s="38"/>
-      <c r="T19" s="41"/>
+    <row r="19" spans="1:21" ht="15" customHeight="1">
+      <c r="P19" s="38"/>
+      <c r="U19" s="41"/>
     </row>
-    <row r="20" spans="1:20" ht="73.5" customHeight="1">
-      <c r="O20" s="38"/>
+    <row r="20" spans="1:21" ht="73.5" customHeight="1">
+      <c r="P20" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="N6:O7"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="C5:P5"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="B5:O5"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="R6:R8"/>
     <mergeCell ref="L6:L8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="Q5:R5"/>
     <mergeCell ref="H6:H8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="G6:G8"/>
   </mergeCells>
+  <conditionalFormatting sqref="B9:B15">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B1048576 B1:B8">
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A9:A15">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A1048576 A1:A8">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
